--- a/reports/集团总公司_现金流量表_2026-12.xlsx
+++ b/reports/集团总公司_现金流量表_2026-12.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>194824500</v>
+        <v>191618072</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>2400494928</v>
+        <v>2358121199</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3879036</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>48526913</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1951820</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>24247887</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>967731</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>12131298</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>781666</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>9700114</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>580521</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>7277676</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>390512</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>4850974</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>290776</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>3638088</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>194766</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>2425978</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>486091</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>6062403</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>243926</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>3048429</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>155021</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1927386</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>529523</v>
+        <v>517784</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>6605390</v>
+        <v>6487631</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3596760</v>
+        <v>3552632</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>44866800</v>
+        <v>44092678</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>198950783</v>
+        <v>205610354</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>119892000</v>
+        <v>117721513</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>1495560000</v>
+        <v>1469858518</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1295685</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>16174810</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>974218</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>12124023</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>645955</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>8087847</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>488248</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>6062089</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>322481</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>4043610</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>245513</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>3046999</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>24178220</v>
+        <v>23615827</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>301604600</v>
+        <v>295925822</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>11189920</v>
+        <v>11024534</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>139585600</v>
+        <v>137049588</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>5095410</v>
+        <v>4988573</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>63561300</v>
+        <v>62354819</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>160355550</v>
+        <v>161322547</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>38595233</v>
+        <v>44287807</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>247200</v>
+        <v>241825</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>2966400</v>
+        <v>2916412</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2163000</v>
+        <v>2117440</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>25956000</v>
+        <v>25486242</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1318400</v>
+        <v>1297165</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>15820800</v>
+        <v>15542620</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2410200</v>
+        <v>2359265</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20600000</v>
+        <v>20149350</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>247200000</v>
+        <v>242234187</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2987000</v>
+        <v>2932654</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>35844000</v>
+        <v>35076416</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14626000</v>
+        <v>14276359</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>175512000</v>
+        <v>172074939</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>535600</v>
+        <v>523966</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>6427200</v>
+        <v>6312016</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>21135600</v>
+        <v>20673316</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18725400</v>
+        <v>-18314051</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4841000</v>
+        <v>4769592</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>58092000</v>
+        <v>57101846</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7725000</v>
+        <v>7623187</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>92700000</v>
+        <v>91051906</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7725000</v>
+        <v>7552675</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>92700000</v>
+        <v>91103157</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>247200</v>
+        <v>244203</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>2966400</v>
+        <v>2915494</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12813200</v>
+        <v>12636982</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6283000</v>
+        <v>6196671</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>75396000</v>
+        <v>74102385</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6283000</v>
+        <v>6161477</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>75396000</v>
+        <v>74089952</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1030000</v>
+        <v>1012648</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>12360000</v>
+        <v>12146726</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>896100</v>
+        <v>878309</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>10753200</v>
+        <v>10569443</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>128750</v>
+        <v>126974</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>1545000</v>
+        <v>1517504</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7441750</v>
+        <v>7336293</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5371450</v>
+        <v>5300689</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>25241283</v>
+        <v>31274445</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>25241283</v>
+        <v>31274445</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
